--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/00840B-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/00840B-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0FF67ACC-0920-4D76-A8C2-6DFDB8001E04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B35DBB6D-F8F3-417D-AAE8-BE2DA5E3B961}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{3FE3C894-801B-4899-9098-C8AF30D1B387}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{410AAAB3-BD81-48B6-A045-40FB19EE427A}"/>
   </bookViews>
   <sheets>
     <sheet name="00840B-dividend-20260225_0_4" sheetId="2" r:id="rId1"/>
@@ -1666,25 +1666,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D3AD924-9DE3-4288-B5CB-BB4678BD5CCF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8D48B51-9B00-443B-8C51-9AE704EDD2F5}">
   <dimension ref="A1:R50"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="8.77734375" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="8.33203125" customWidth="1"/>
-    <col min="7" max="9" width="8" customWidth="1"/>
-    <col min="10" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.44140625" customWidth="1"/>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="2" max="2" width="10.875" customWidth="1"/>
+    <col min="3" max="3" width="11.375" customWidth="1"/>
+    <col min="4" max="4" width="10.375" customWidth="1"/>
+    <col min="5" max="5" width="9.875" customWidth="1"/>
+    <col min="6" max="6" width="10.375" customWidth="1"/>
+    <col min="7" max="9" width="9.875" customWidth="1"/>
+    <col min="10" max="10" width="10.375" customWidth="1"/>
+    <col min="11" max="13" width="9.875" customWidth="1"/>
+    <col min="14" max="14" width="10.375" customWidth="1"/>
+    <col min="15" max="17" width="9.875" customWidth="1"/>
+    <col min="18" max="18" width="11.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -1712,7 +1712,7 @@
       <c r="Q1" s="32"/>
       <c r="R1" s="24"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
@@ -1742,7 +1742,7 @@
       <c r="Q2" s="34"/>
       <c r="R2" s="35"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="25" t="s">
         <v>2</v>
       </c>
@@ -1788,7 +1788,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="27"/>
       <c r="B4" s="28"/>
       <c r="C4" s="7"/>
@@ -1838,7 +1838,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="39">
         <v>2026</v>
       </c>
@@ -1892,7 +1892,7 @@
         <v>4.68</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="41"/>
       <c r="B6" s="42"/>
       <c r="C6" s="44"/>
@@ -1918,7 +1918,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>26</v>
       </c>
@@ -1974,7 +1974,7 @@
         <v>0.39</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
         <v>26</v>
       </c>
@@ -2030,7 +2030,7 @@
         <v>0.39</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="49">
         <v>2025</v>
       </c>
@@ -2084,7 +2084,7 @@
         <v>4.8</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
         <v>26</v>
       </c>
@@ -2140,7 +2140,7 @@
         <v>0.39</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
         <v>26</v>
       </c>
@@ -2196,7 +2196,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
         <v>26</v>
       </c>
@@ -2252,7 +2252,7 @@
         <v>0.35</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="19" t="s">
         <v>26</v>
       </c>
@@ -2308,7 +2308,7 @@
         <v>0.36</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="19" t="s">
         <v>26</v>
       </c>
@@ -2364,7 +2364,7 @@
         <v>0.38</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
         <v>26</v>
       </c>
@@ -2420,7 +2420,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
         <v>26</v>
       </c>
@@ -2476,7 +2476,7 @@
         <v>0.43</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="19" t="s">
         <v>26</v>
       </c>
@@ -2532,7 +2532,7 @@
         <v>0.43</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="19" t="s">
         <v>26</v>
       </c>
@@ -2588,7 +2588,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
         <v>26</v>
       </c>
@@ -2644,7 +2644,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="19" t="s">
         <v>26</v>
       </c>
@@ -2700,7 +2700,7 @@
         <v>0.41</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="19" t="s">
         <v>26</v>
       </c>
@@ -2756,7 +2756,7 @@
         <v>0.41</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="51">
         <v>2024</v>
       </c>
@@ -2810,7 +2810,7 @@
         <v>4.49</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
         <v>26</v>
       </c>
@@ -2866,7 +2866,7 @@
         <v>0.37</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
         <v>26</v>
       </c>
@@ -2922,7 +2922,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>26</v>
       </c>
@@ -2978,7 +2978,7 @@
         <v>1.06</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
         <v>26</v>
       </c>
@@ -3034,7 +3034,7 @@
         <v>1.03</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>26</v>
       </c>
@@ -3090,7 +3090,7 @@
         <v>1.03</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="49">
         <v>2023</v>
       </c>
@@ -3144,7 +3144,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="19" t="s">
         <v>26</v>
       </c>
@@ -3200,7 +3200,7 @@
         <v>1.07</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="19" t="s">
         <v>26</v>
       </c>
@@ -3256,7 +3256,7 @@
         <v>1.01</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="19" t="s">
         <v>26</v>
       </c>
@@ -3312,7 +3312,7 @@
         <v>0.98</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="19" t="s">
         <v>26</v>
       </c>
@@ -3368,7 +3368,7 @@
         <v>1.03</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="51">
         <v>2022</v>
       </c>
@@ -3422,7 +3422,7 @@
         <v>2.93</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="11" t="s">
         <v>26</v>
       </c>
@@ -3478,7 +3478,7 @@
         <v>1.02</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="11" t="s">
         <v>26</v>
       </c>
@@ -3534,7 +3534,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
         <v>26</v>
       </c>
@@ -3590,7 +3590,7 @@
         <v>0.67</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="11" t="s">
         <v>26</v>
       </c>
@@ -3646,7 +3646,7 @@
         <v>0.39</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="49">
         <v>2021</v>
       </c>
@@ -3700,7 +3700,7 @@
         <v>2.84</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="19" t="s">
         <v>26</v>
       </c>
@@ -3756,7 +3756,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="19" t="s">
         <v>26</v>
       </c>
@@ -3812,7 +3812,7 @@
         <v>0.67</v>
       </c>
     </row>
-    <row r="41" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="19" t="s">
         <v>26</v>
       </c>
@@ -3868,7 +3868,7 @@
         <v>0.74</v>
       </c>
     </row>
-    <row r="42" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="19" t="s">
         <v>26</v>
       </c>
@@ -3924,7 +3924,7 @@
         <v>0.73</v>
       </c>
     </row>
-    <row r="43" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="51">
         <v>2020</v>
       </c>
@@ -3978,7 +3978,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="44" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="11" t="s">
         <v>26</v>
       </c>
@@ -4034,7 +4034,7 @@
         <v>0.67</v>
       </c>
     </row>
-    <row r="45" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="11" t="s">
         <v>26</v>
       </c>
@@ -4090,7 +4090,7 @@
         <v>0.67</v>
       </c>
     </row>
-    <row r="46" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="11" t="s">
         <v>26</v>
       </c>
@@ -4146,7 +4146,7 @@
         <v>0.72</v>
       </c>
     </row>
-    <row r="47" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="11" t="s">
         <v>26</v>
       </c>
@@ -4202,7 +4202,7 @@
         <v>0.74</v>
       </c>
     </row>
-    <row r="48" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="49">
         <v>2019</v>
       </c>
@@ -4256,7 +4256,7 @@
         <v>0.98</v>
       </c>
     </row>
-    <row r="49" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A49" s="19" t="s">
         <v>26</v>
       </c>
@@ -4312,7 +4312,7 @@
         <v>0.98</v>
       </c>
     </row>
-    <row r="50" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A50" s="51" t="s">
         <v>93</v>
       </c>
